--- a/data/TTS/最新版班表/TTS_TM.xlsx
+++ b/data/TTS/最新版班表/TTS_TM.xlsx
@@ -968,9 +968,9 @@
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
-          <t>15:15
-SM0524
-23:15
+          <t>16:30
+STD6
+24:30
 8:00</t>
         </is>
       </c>
@@ -1002,10 +1002,10 @@
       </c>
       <c r="U7" s="1" t="inlineStr">
         <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
+          <t>14:15
+SM0526
+23:35
+9:20</t>
         </is>
       </c>
       <c r="V7" s="1" t="inlineStr">
@@ -1040,10 +1040,10 @@
       </c>
       <c r="Z7" s="1" t="inlineStr">
         <is>
-          <t>13:50
-SM0512
-21:50
-8:00</t>
+          <t>15:15
+SM0529
+23:35
+8:20</t>
         </is>
       </c>
       <c r="AA7" s="1" t="inlineStr">
@@ -1110,10 +1110,10 @@
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>7:10
-SM0015
-16:48
-9:38</t>
+          <t>5:57
+SM0006
+13:57
+8:00</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -1140,18 +1140,18 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>8:30
-SM1023
-16:30
+          <t>5:02
+SM0001
+13:02
 8:00</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>9:15
-SM0028
-17:48
-8:33</t>
+          <t>5:37
+SM1003
+13:37
+8:00</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -1211,18 +1211,18 @@
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>16:15
-SM0535
-24:15
+          <t>5:37
+SM0003
+13:37
 8:00</t>
         </is>
       </c>
       <c r="U8" s="1" t="inlineStr">
         <is>
-          <t>14:15
-SM0526
-23:35
-9:20</t>
+          <t>5:37
+SM0003
+13:37
+8:00</t>
         </is>
       </c>
       <c r="V8" s="1" t="inlineStr">
@@ -1391,10 +1391,10 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>6:37
-SM2012
-14:43
-8:06</t>
+          <t>10:40
+SM0033
+19:43
+9:03</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1941,65 +1941,118 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
+          <t>14:00
+STD5
+22:00
+8:00</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>12:50
+SM2502
+20:50
+8:00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>10:00
+STD3
+18:00
+8:00</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>9:40
+SM5902
+17:43
+8:03</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>10:00
+STD3
+18:00
+8:00</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>9:40
+SM0031
+17:43
+8:03</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>11:50
+SM0038
+20:28
+8:38</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>8:15
+SM1022
+16:15
+8:00</t>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
           <t>8:40
 SM2024
 17:00
 8:20</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>8:50
-SM1025
-16:50
-8:00</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>10:00
-STD3
-18:00
-8:00</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>9:40
-SM5902
-17:43
-8:03</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
-        </is>
-      </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="R12" s="1" t="inlineStr">
+        <is>
+          <t>9:15
+SM0028
+17:48
+8:33</t>
+        </is>
+      </c>
+      <c r="S12" s="1" t="inlineStr">
         <is>
           <t>9:40
 SM0031
@@ -2007,15 +2060,483 @@
 8:03</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="V12" s="1" t="inlineStr">
+        <is>
+          <t>12:15
+SM0506
+21:00
+8:45</t>
+        </is>
+      </c>
+      <c r="W12" s="1" t="inlineStr">
+        <is>
+          <t>13:48
+SM1509
+21:48
+8:00</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="inlineStr">
+        <is>
+          <t>13:50
+DO2W
+SM3512
+21:50
+8:00</t>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
+          <t>10:40
+SM0034
+18:53
+8:13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AA12" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+SM0502
+20:50
+8:10</t>
+        </is>
+      </c>
+      <c r="AB12" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+SM0507
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AD12" s="1" t="inlineStr">
+        <is>
+          <t>8:50
+SM2025
+16:50
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A019078</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>陳韻茹</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>15:30
+SM0525
+23:30
+8:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>12:55
+SM0505
+21:00
+8:05</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+SM0502
+20:50
+8:10</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>13:30
+SM0512
+21:48
+8:18</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+STD2
+15:30
+8:00</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>7:10
+SM0015
+16:48
+9:38</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t>10:00
+MTM
+18:00
+8:00</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>6:47
+SM2013
+14:47
+8:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>6:47
+SM0014
+16:25
+9:38</t>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>6:37
+SM3012
+14:37
+8:00</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>5:57
+SM0006
+13:57
+8:00</t>
+        </is>
+      </c>
+      <c r="T13" s="1" t="inlineStr">
+        <is>
+          <t>5:00
+STD1
+13:00
+8:00</t>
+        </is>
+      </c>
+      <c r="U13" s="1" t="inlineStr">
+        <is>
+          <t>10:00
+STD3
+18:00
+8:00</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="W13" s="1" t="inlineStr">
+        <is>
+          <t>7:37
+SM3019
+15:37
+8:00</t>
+        </is>
+      </c>
+      <c r="X13" s="1" t="inlineStr">
+        <is>
+          <t>14:50
+SM1522
+22:53
+8:03</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z13" s="1" t="inlineStr">
+        <is>
+          <t>5:52
+SM0004
+13:52
+8:00</t>
+        </is>
+      </c>
+      <c r="AA13" s="1" t="inlineStr">
+        <is>
+          <t>7:10
+SM0015
+16:48
+9:38</t>
+        </is>
+      </c>
+      <c r="AB13" s="1" t="inlineStr">
+        <is>
+          <t>7:10
+SM1015
+16:48
+9:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AD13" s="1" t="inlineStr">
+        <is>
+          <t>7:12
+SM2017
+15:12
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A019081</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>陳怡妏</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>7:50
+SM1021
+15:50
+8:00</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>5:52
+SM2004
+13:52
+8:00</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>5:57
+SM0006
+13:57
+8:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>5:52
+SM3004
+14:00
+8:08</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>5:27
+DO2W
+SM1002
+13:27
+8:00</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>6:10
+SM0008
+14:10
+8:00</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>5:00
+STD1
+13:00
+8:00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>5:57
+SM0006
+13:57
+8:00</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>6:27
+SM1009
+14:27
+8:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>7:50
+SM0021
+15:50
+8:00</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>7:07
+SM1016
+15:07
+8:00</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>7:37
+SM0019
+16:08
+8:31</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="U14" s="1" t="inlineStr">
+        <is>
+          <t>14:27
+SM1518
+22:35
+8:08</t>
+        </is>
+      </c>
+      <c r="V14" s="1" t="inlineStr">
+        <is>
+          <t>15:15
+SM1523
+23:15
+8:00</t>
+        </is>
+      </c>
+      <c r="W14" s="1" t="inlineStr">
+        <is>
+          <t>14:00
+STD5
+22:00
+8:00</t>
+        </is>
+      </c>
+      <c r="X14" s="1" t="inlineStr">
+        <is>
+          <t>DO2W
+DO2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z14" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AA14" s="1" t="inlineStr">
+        <is>
+          <t>14:35
+SM0518
+22:35
+8:00</t>
+        </is>
+      </c>
+      <c r="AB14" s="1" t="inlineStr">
         <is>
           <t>11:50
 SM0038
@@ -2023,527 +2544,6 @@
 8:38</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P12" s="1" t="inlineStr">
-        <is>
-          <t>7:50
-SM0021
-15:50
-8:00</t>
-        </is>
-      </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>7:07
-SM1016
-15:07
-8:00</t>
-        </is>
-      </c>
-      <c r="R12" s="1" t="inlineStr">
-        <is>
-          <t>7:37
-SM0019
-16:08
-8:31</t>
-        </is>
-      </c>
-      <c r="S12" s="1" t="inlineStr">
-        <is>
-          <t>9:40
-SM0031
-17:43
-8:03</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="V12" s="1" t="inlineStr">
-        <is>
-          <t>12:15
-SM0506
-21:00
-8:45</t>
-        </is>
-      </c>
-      <c r="W12" s="1" t="inlineStr">
-        <is>
-          <t>13:48
-SM1509
-21:48
-8:00</t>
-        </is>
-      </c>
-      <c r="X12" s="1" t="inlineStr">
-        <is>
-          <t>13:50
-DO2W
-SM3512
-21:50
-8:00</t>
-        </is>
-      </c>
-      <c r="Y12" s="1" t="inlineStr">
-        <is>
-          <t>10:40
-SM0034
-18:53
-8:13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AA12" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-SM0502
-20:50
-8:10</t>
-        </is>
-      </c>
-      <c r="AB12" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-SM0507
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AD12" s="1" t="inlineStr">
-        <is>
-          <t>8:15
-SM1022
-16:15
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A019078</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>陳韻茹</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>15:30
-SM0525
-23:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>12:55
-SM0505
-21:00
-8:05</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-SM0502
-20:50
-8:10</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>13:30
-SM0512
-21:48
-8:18</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-STD2
-15:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L13" s="1" t="inlineStr">
-        <is>
-          <t>7:10
-SM0015
-16:48
-9:38</t>
-        </is>
-      </c>
-      <c r="M13" s="1" t="inlineStr">
-        <is>
-          <t>10:00
-MTM
-18:00
-8:00</t>
-        </is>
-      </c>
-      <c r="N13" s="1" t="inlineStr">
-        <is>
-          <t>6:47
-SM2013
-14:47
-8:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P13" s="1" t="inlineStr">
-        <is>
-          <t>6:47
-SM0014
-16:25
-9:38</t>
-        </is>
-      </c>
-      <c r="Q13" s="1" t="inlineStr">
-        <is>
-          <t>6:37
-SM3012
-14:37
-8:00</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S13" s="1" t="inlineStr">
-        <is>
-          <t>5:57
-SM0006
-13:57
-8:00</t>
-        </is>
-      </c>
-      <c r="T13" s="1" t="inlineStr">
-        <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
-        </is>
-      </c>
-      <c r="U13" s="1" t="inlineStr">
-        <is>
-          <t>10:00
-STD3
-18:00
-8:00</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="W13" s="1" t="inlineStr">
-        <is>
-          <t>7:37
-SM3019
-15:37
-8:00</t>
-        </is>
-      </c>
-      <c r="X13" s="1" t="inlineStr">
-        <is>
-          <t>14:50
-SM1522
-22:53
-8:03</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z13" s="1" t="inlineStr">
-        <is>
-          <t>5:52
-SM0004
-13:52
-8:00</t>
-        </is>
-      </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t>7:10
-SM0015
-16:48
-9:38</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t>7:10
-SM1015
-16:48
-9:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AD13" s="1" t="inlineStr">
-        <is>
-          <t>7:22
-SM0018
-16:55
-9:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A019081</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>陳怡妏</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>7:50
-SM1021
-15:50
-8:00</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>5:52
-SM2004
-13:52
-8:00</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>5:57
-SM0006
-13:57
-8:00</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="inlineStr">
-        <is>
-          <t>5:52
-SM3004
-14:00
-8:08</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>5:27
-DO2W
-SM1002
-13:27
-8:00</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>6:10
-SM0008
-14:10
-8:00</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>10:00
-STD3
-18:00
-8:00</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M14" s="1" t="inlineStr">
-        <is>
-          <t>5:57
-SM0006
-13:57
-8:00</t>
-        </is>
-      </c>
-      <c r="N14" s="1" t="inlineStr">
-        <is>
-          <t>6:27
-SM1009
-14:27
-8:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="P14" s="1" t="inlineStr">
-        <is>
-          <t>8:15
-SM1022
-16:15
-8:00</t>
-        </is>
-      </c>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>8:40
-SM2024
-17:00
-8:20</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t>9:15
-SM0028
-17:48
-8:33</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="U14" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-SM2531
-24:10
-8:30</t>
-        </is>
-      </c>
-      <c r="V14" s="1" t="inlineStr">
-        <is>
-          <t>15:15
-SM1523
-23:15
-8:00</t>
-        </is>
-      </c>
-      <c r="W14" s="1" t="inlineStr">
-        <is>
-          <t>14:00
-STD5
-22:00
-8:00</t>
-        </is>
-      </c>
-      <c r="X14" s="1" t="inlineStr">
-        <is>
-          <t>DO2W
-DO2</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z14" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA14" s="1" t="inlineStr">
-        <is>
-          <t>16:15
-SM0535
-24:15
-8:00</t>
-        </is>
-      </c>
-      <c r="AB14" s="1" t="inlineStr">
-        <is>
-          <t>11:50
-SM0038
-20:28
-8:38</t>
-        </is>
-      </c>
       <c r="AC14" s="1" t="inlineStr">
         <is>
           <t>15:27
@@ -2584,9 +2584,9 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>16:10
-SM0531
-24:10
+          <t>13:08
+SM0507
+21:08
 8:00</t>
         </is>
       </c>
@@ -2944,9 +2944,9 @@
       </c>
       <c r="AA16" s="1" t="inlineStr">
         <is>
-          <t>14:35
-SM0518
-22:35
+          <t>16:15
+SM0535
+24:15
 8:00</t>
         </is>
       </c>
@@ -3074,9 +3074,9 @@
       </c>
       <c r="P17" s="1" t="inlineStr">
         <is>
-          <t>16:30
-STD6
-24:30
+          <t>15:15
+SM0524
+23:15
 8:00</t>
         </is>
       </c>
@@ -3103,221 +3103,221 @@
       </c>
       <c r="T17" s="1" t="inlineStr">
         <is>
+          <t>16:15
+SM0535
+24:15
+8:00</t>
+        </is>
+      </c>
+      <c r="U17" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="V17" s="1" t="inlineStr">
+        <is>
+          <t>14:50
+SM0519
+22:55
+8:05</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X17" s="1" t="inlineStr">
+        <is>
+          <t>DO2W
+DO2</t>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="Z17" s="1" t="inlineStr">
+        <is>
+          <t>14:05
+SM0517
+22:05
+8:00</t>
+        </is>
+      </c>
+      <c r="AA17" s="1" t="inlineStr">
+        <is>
+          <t>16:25
+SM0533
+24:25
+8:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AD17" s="1" t="inlineStr">
+        <is>
+          <t>6:07
+SM2007
+14:15
+8:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A019304</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>韓書華</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>16:29
+SM1534
+24:29
+8:00</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>15:15
+SM2523
+23:15
+8:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>14:08
+SM1516
+22:08
+8:00</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>15:30
+SM0530
+23:55
+8:25</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+DO2W
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>16:10
+SM3531
+24:10
+8:00</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>6:27
+SM0009
+14:27
+8:00</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="inlineStr">
+        <is>
+          <t>9:15
+SM0028
+17:48
+8:33</t>
+        </is>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>5:57
+SM2006
+13:57
+8:00</t>
+        </is>
+      </c>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+STD2
+15:30
+8:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R18" s="1" t="inlineStr">
+        <is>
+          <t>6:07
+SM0007
+15:28
+9:21</t>
+        </is>
+      </c>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+STD2
+15:30
+8:00</t>
+        </is>
+      </c>
+      <c r="T18" s="1" t="inlineStr">
+        <is>
           <t>7:37
 SM0019
 16:08
 8:31</t>
-        </is>
-      </c>
-      <c r="U17" s="1" t="inlineStr">
-        <is>
-          <t>5:37
-SM0003
-13:37
-8:00</t>
-        </is>
-      </c>
-      <c r="V17" s="1" t="inlineStr">
-        <is>
-          <t>14:50
-SM0519
-22:55
-8:05</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X17" s="1" t="inlineStr">
-        <is>
-          <t>DO2W
-DO2</t>
-        </is>
-      </c>
-      <c r="Y17" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Z17" s="1" t="inlineStr">
-        <is>
-          <t>14:05
-SM0517
-22:05
-8:00</t>
-        </is>
-      </c>
-      <c r="AA17" s="1" t="inlineStr">
-        <is>
-          <t>16:25
-SM0533
-24:25
-8:00</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AD17" s="1" t="inlineStr">
-        <is>
-          <t>6:07
-SM2007
-14:15
-8:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A019304</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>韓書華</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>16:29
-SM1534
-24:29
-8:00</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>15:15
-SM2523
-23:15
-8:00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>14:08
-SM1516
-22:08
-8:00</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>15:30
-SM0530
-23:55
-8:25</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-DO2W
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>16:10
-SM3531
-24:10
-8:00</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="M18" s="1" t="inlineStr">
-        <is>
-          <t>6:27
-SM0009
-14:27
-8:00</t>
-        </is>
-      </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>9:15
-SM0028
-17:48
-8:33</t>
-        </is>
-      </c>
-      <c r="O18" s="1" t="inlineStr">
-        <is>
-          <t>5:57
-SM2006
-13:57
-8:00</t>
-        </is>
-      </c>
-      <c r="P18" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-STD2
-15:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R18" s="1" t="inlineStr">
-        <is>
-          <t>6:07
-SM0007
-15:28
-9:21</t>
-        </is>
-      </c>
-      <c r="S18" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-STD2
-15:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T18" s="1" t="inlineStr">
-        <is>
-          <t>5:37
-SM0003
-13:37
-8:00</t>
         </is>
       </c>
       <c r="U18" s="1" t="inlineStr">
@@ -3620,9 +3620,9 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>7:37
-SM0020
-15:37
+          <t>6:07
+SM3007
+14:07
 8:00</t>
         </is>
       </c>
@@ -3760,9 +3760,9 @@
       </c>
       <c r="W20" s="1" t="inlineStr">
         <is>
-          <t>16:29
-SM2534
-24:29
+          <t>13:08
+SM2507
+21:08
 8:00</t>
         </is>
       </c>
@@ -3882,10 +3882,10 @@
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>14:15
-SM1526
-23:35
-9:20</t>
+          <t>9:30
+SM0030
+17:43
+8:13</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -4045,10 +4045,10 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>9:15
-SM0028
-17:48
-8:33</t>
+          <t>9:10
+SM1027
+17:10
+8:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4109,10 +4109,10 @@
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>16:15
-SM0535
-24:15
-8:00</t>
+          <t>12:40
+SM0502
+20:50
+8:10</t>
         </is>
       </c>
       <c r="N22" s="1" t="inlineStr">
@@ -4757,10 +4757,10 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>7:12
-SM1017
-15:48
-8:36</t>
+          <t>5:02
+SM0001
+13:02
+8:00</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -5318,9 +5318,9 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>5:02
-SM0001
-13:02
+          <t>6:10
+SM0008
+14:10
 8:00</t>
         </is>
       </c>
@@ -5567,10 +5567,10 @@
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>6:10
-SM0008
-14:10
-8:00</t>
+          <t>10:50
+SM0034
+18:55
+8:05</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -6186,9 +6186,9 @@
       </c>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>5:02
-SM0001
-13:02
+          <t>8:30
+SM1023
+16:30
 8:00</t>
         </is>
       </c>
@@ -6220,10 +6220,10 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>5:02
-SM0001
-13:02
-8:00</t>
+          <t>7:12
+SM1017
+15:48
+8:36</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -6430,10 +6430,10 @@
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>10:40
-SM0033
-19:43
-9:03</t>
+          <t>6:37
+SM2012
+14:43
+8:06</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -6590,9 +6590,9 @@
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>16:29
-SM1534
-24:29
+          <t>6:37
+SM2012
+14:37
 8:00</t>
         </is>
       </c>
@@ -6906,9 +6906,9 @@
       </c>
       <c r="W35" s="1" t="inlineStr">
         <is>
-          <t>13:08
-SM2507
-21:08
+          <t>10:00
+SM0032
+18:00
 8:00</t>
         </is>
       </c>
@@ -6984,10 +6984,10 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>9:10
-SM0027
-17:48
-8:38</t>
+          <t>5:02
+SM0001
+13:02
+8:00</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
@@ -7274,9 +7274,9 @@
       </c>
       <c r="P37" s="1" t="inlineStr">
         <is>
-          <t>16:10
-SM3531
-24:10
+          <t>16:29
+SM2534
+24:29
 8:00</t>
         </is>
       </c>
@@ -7395,17 +7395,17 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>14:00
-STD5
-22:00
-8:00</t>
+          <t>8:40
+SM2024
+17:00
+8:20</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>12:50
-SM2502
-20:50
+          <t>8:50
+SM1025
+16:50
 8:00</t>
         </is>
       </c>
@@ -7752,9 +7752,9 @@
       </c>
       <c r="W39" s="1" t="inlineStr">
         <is>
-          <t>10:00
-SM0032
-18:00
+          <t>8:30
+SM0023
+16:30
 8:00</t>
         </is>
       </c>
@@ -7894,10 +7894,10 @@
       </c>
       <c r="M40" s="1" t="inlineStr">
         <is>
-          <t>12:40
-SM0502
-20:50
-8:10</t>
+          <t>16:15
+SM0535
+24:15
+8:00</t>
         </is>
       </c>
       <c r="N40" s="1" t="inlineStr">
@@ -7915,18 +7915,18 @@
       </c>
       <c r="P40" s="1" t="inlineStr">
         <is>
-          <t>16:29
-SM2534
-24:29
+          <t>16:10
+SM3531
+24:10
 8:00</t>
         </is>
       </c>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>13:15
-SM2509
-21:48
-8:33</t>
+          <t>14:53
+SM1522
+22:53
+8:00</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr">
@@ -7965,9 +7965,9 @@
       </c>
       <c r="W40" s="1" t="inlineStr">
         <is>
-          <t>8:30
-SM0023
-16:30
+          <t>16:29
+SM2534
+24:29
 8:00</t>
         </is>
       </c>
@@ -7981,10 +7981,10 @@
       </c>
       <c r="Y40" s="1" t="inlineStr">
         <is>
-          <t>16:25
-SM0534
-24:25
-8:00</t>
+          <t>14:22
+SM1516
+22:30
+8:08</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -8884,10 +8884,10 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9:10
-SM1027
-17:10
-8:00</t>
+          <t>9:15
+SM0028
+17:48
+8:33</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -8900,10 +8900,10 @@
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>5:57
-SM0006
-13:57
-8:00</t>
+          <t>7:10
+SM0015
+16:48
+9:38</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
@@ -8934,10 +8934,10 @@
       </c>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>5:37
-SM1003
-13:37
-8:00</t>
+          <t>9:15
+SM0028
+17:48
+8:33</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
@@ -9031,10 +9031,10 @@
       </c>
       <c r="Y45" s="1" t="inlineStr">
         <is>
-          <t>14:22
-SM1516
-22:30
-8:08</t>
+          <t>16:25
+SM0534
+24:25
+8:00</t>
         </is>
       </c>
       <c r="Z45" s="1" t="inlineStr">
@@ -9560,10 +9560,10 @@
       </c>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>9:30
-SM0030
-17:43
-8:13</t>
+          <t>14:15
+SM1526
+23:35
+9:20</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -9795,9 +9795,9 @@
       </c>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>6:10
-SM0008
-14:10
+          <t>13:00
+SM2505
+21:00
 8:00</t>
         </is>
       </c>
@@ -9883,10 +9883,10 @@
       </c>
       <c r="Z49" s="1" t="inlineStr">
         <is>
-          <t>15:15
-SM0529
-23:35
-8:20</t>
+          <t>13:50
+SM0512
+21:50
+8:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -11365,9 +11365,9 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>6:07
-SM3007
-14:07
+          <t>7:37
+SM0020
+15:37
 8:00</t>
         </is>
       </c>
@@ -11417,10 +11417,10 @@
       </c>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>10:50
-SM0034
-18:55
-8:05</t>
+          <t>7:37
+SM0019
+16:08
+8:31</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -11462,10 +11462,10 @@
       </c>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>14:53
-SM1522
-22:53
-8:00</t>
+          <t>13:15
+SM2509
+21:48
+8:33</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -11588,10 +11588,10 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>6:10
-SM0008
-14:10
-8:00</t>
+          <t>9:10
+SM0027
+17:48
+8:38</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -11634,23 +11634,842 @@
       </c>
       <c r="K58" s="1" t="inlineStr">
         <is>
+          <t>6:10
+SM0008
+14:10
+8:00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N58" s="1" t="inlineStr">
+        <is>
+          <t>13:50
+SM0512
+21:50
+8:00</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>13:30
+SM0508
+21:30
+8:00</t>
+        </is>
+      </c>
+      <c r="P58" s="1" t="inlineStr">
+        <is>
+          <t>12:00
+STD4
+20:00
+8:00</t>
+        </is>
+      </c>
+      <c r="Q58" s="1" t="inlineStr">
+        <is>
+          <t>12:43
+SM1503
+20:43
+8:00</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S58" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+SM0502
+20:50
+8:10</t>
+        </is>
+      </c>
+      <c r="T58" s="1" t="inlineStr">
+        <is>
+          <t>14:00
+STD5
+22:00
+8:00</t>
+        </is>
+      </c>
+      <c r="U58" s="1" t="inlineStr">
+        <is>
+          <t>13:50
+SM0512
+21:50
+8:00</t>
+        </is>
+      </c>
+      <c r="V58" s="1" t="inlineStr">
+        <is>
+          <t>13:30
+SM0508
+21:30
+8:00</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X58" s="1" t="inlineStr">
+        <is>
+          <t>12:43
+DO2W
+SM1503
+20:43
+8:00</t>
+        </is>
+      </c>
+      <c r="Y58" s="1" t="inlineStr">
+        <is>
+          <t>12:33
+SM0504
+20:43
+8:10</t>
+        </is>
+      </c>
+      <c r="Z58" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+SM0507
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AC58" s="1" t="inlineStr">
+        <is>
+          <t>13:30
+SM0508
+21:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AD58" s="1" t="inlineStr">
+        <is>
+          <t>9:30
+SM1030
+17:30
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A021739</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>林佑任</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD6
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>15:55
+SM1529
+23:55
+8:00</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>14:35
+SM0518
+22:35
+8:00</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>12:55
+SM0505
+21:00
+8:05</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J59" s="1" t="inlineStr">
+        <is>
+          <t>8:15
+SM2022
+16:15
+8:00</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+TOWN
+16:30
+8:00</t>
+        </is>
+      </c>
+      <c r="M59" s="1" t="inlineStr">
+        <is>
+          <t>6:47
+SM0013
+14:48
+8:01</t>
+        </is>
+      </c>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>5:02
+SM0001
+13:02
+8:00</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>5:27
+SM0002
+13:27
+8:00</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R59" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+STD2
+15:30
+8:00</t>
+        </is>
+      </c>
+      <c r="S59" s="1" t="inlineStr">
+        <is>
+          <t>6:37
+SM0012
+14:43
+8:06</t>
+        </is>
+      </c>
+      <c r="T59" s="1" t="inlineStr">
+        <is>
+          <t>6:10
+SM0008
+14:10
+8:00</t>
+        </is>
+      </c>
+      <c r="U59" s="1" t="inlineStr">
+        <is>
+          <t>7:37
+SM1019
+15:43
+8:06</t>
+        </is>
+      </c>
+      <c r="V59" s="1" t="inlineStr">
+        <is>
+          <t>5:00
+STD1
+13:00
+8:00</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z59" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AA59" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AB59" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AC59" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A021747</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>林美伶</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>14:10
+SM0527
+23:35
+9:25</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>13:50
+SM0512
+21:50
+8:00</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>12:50
+SM1518
+22:20
+9:30</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>16:25
+SM1533
+24:25
+8:00</t>
+        </is>
+      </c>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>16:15
+DO2W
+SM2534
+24:15
+8:00</t>
+        </is>
+      </c>
+      <c r="J60" s="1" t="inlineStr">
+        <is>
+          <t>14:00
+STD5
+22:00
+8:00</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="L60" s="1" t="inlineStr">
+        <is>
+          <t>14:15
+SM0526
+23:35
+9:20</t>
+        </is>
+      </c>
+      <c r="M60" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+SM0507
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>14:15
+SM0526
+23:35
+9:20</t>
+        </is>
+      </c>
+      <c r="O60" s="1" t="inlineStr">
+        <is>
+          <t>13:43
+SM1512
+21:43
+8:00</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>14:50
+SM2521
+22:50
+8:00</t>
+        </is>
+      </c>
+      <c r="R60" s="1" t="inlineStr">
+        <is>
+          <t>12:50
+SM2502
+20:50
+8:00</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="U60" s="1" t="inlineStr">
+        <is>
+          <t>11:50
+SM0038
+20:28
+8:38</t>
+        </is>
+      </c>
+      <c r="V60" s="1" t="inlineStr">
+        <is>
+          <t>10:40
+SM0033
+19:43
+9:03</t>
+        </is>
+      </c>
+      <c r="W60" s="1" t="inlineStr">
+        <is>
+          <t>8:50
+SM2025
+16:50
+8:00</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z60" s="1" t="inlineStr">
+        <is>
+          <t>6:47
+SM0013
+14:48
+8:01</t>
+        </is>
+      </c>
+      <c r="AA60" s="1" t="inlineStr">
+        <is>
+          <t>5:27
+SM0002
+13:27
+8:00</t>
+        </is>
+      </c>
+      <c r="AB60" s="1" t="inlineStr">
+        <is>
+          <t>5:37
+SM0003
+13:37
+8:00</t>
+        </is>
+      </c>
+      <c r="AC60" s="1" t="inlineStr">
+        <is>
+          <t>5:00
+STD1
+13:00
+8:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A021794</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>狄君璞</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>5:52
+SM0004
+13:52
+8:00</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>5:02
+SM0001
+13:02
+8:00</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J61" s="1" t="inlineStr">
+        <is>
+          <t>12:00
+STD4
+20:00
+8:00</t>
+        </is>
+      </c>
+      <c r="K61" s="1" t="inlineStr">
+        <is>
+          <t>12:00
+STD4
+20:00
+8:00</t>
+        </is>
+      </c>
+      <c r="L61" s="1" t="inlineStr">
+        <is>
+          <t>16:25
+SM0533
+24:25
+8:00</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>15:50
+SM1535
+24:15
+8:25</t>
+        </is>
+      </c>
+      <c r="O61" s="1" t="inlineStr">
+        <is>
+          <t>15:15
+SM1523
+23:15
+8:00</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>14:15
+SM1517
+22:25
+8:10</t>
+        </is>
+      </c>
+      <c r="R61" s="1" t="inlineStr">
+        <is>
+          <t>15:15
+SM2523
+23:15
+8:00</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="U61" s="1" t="inlineStr">
+        <is>
+          <t>14:08
+SM1516
+22:08
+8:00</t>
+        </is>
+      </c>
+      <c r="V61" s="1" t="inlineStr">
+        <is>
+          <t>15:27
+SM0530
+23:55
+8:28</t>
+        </is>
+      </c>
+      <c r="W61" s="1" t="inlineStr">
+        <is>
+          <t>16:10
+SM3531
+24:10
+8:00</t>
+        </is>
+      </c>
+      <c r="X61" s="1" t="inlineStr">
+        <is>
+          <t>14:50
+DO2W
+SM1524
+22:50
+8:00</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z61" s="1" t="inlineStr">
+        <is>
+          <t>9:40
+SM0031
+17:43
+8:03</t>
+        </is>
+      </c>
+      <c r="AA61" s="1" t="inlineStr">
+        <is>
+          <t>6:27
+SM0009
+14:27
+8:00</t>
+        </is>
+      </c>
+      <c r="AB61" s="1" t="inlineStr">
+        <is>
+          <t>6:10
+SM0008
+14:10
+8:00</t>
+        </is>
+      </c>
+      <c r="AC61" s="1" t="inlineStr">
+        <is>
+          <t>7:00
+STD2
+15:00
+8:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A021811</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>劉妍利</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>6:47
+SM1013
+14:47
+8:00</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>6:37
+SM0012
+14:43
+8:06</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
           <t>7:37
 SM0019
 16:08
 8:31</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="N58" s="1" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>11:40
+SM2504
+20:48
+9:08</t>
+        </is>
+      </c>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+DO2W
+SM2507
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="J62" s="1" t="inlineStr">
+        <is>
+          <t>13:08
+SM0507
+21:08
+8:00</t>
+        </is>
+      </c>
+      <c r="K62" s="1" t="inlineStr">
         <is>
           <t>13:50
 SM0512
@@ -11658,15 +12477,17 @@
 8:00</t>
         </is>
       </c>
-      <c r="O58" s="1" t="inlineStr">
-        <is>
-          <t>13:30
-SM0508
-21:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P58" s="1" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
         <is>
           <t>14:00
 STD5
@@ -11674,20 +12495,90 @@
 8:00</t>
         </is>
       </c>
-      <c r="Q58" s="1" t="inlineStr">
-        <is>
-          <t>12:43
-SM1503
-20:43
-8:00</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S58" s="1" t="inlineStr">
+      <c r="O62" s="1" t="inlineStr">
+        <is>
+          <t>15:00
+SM0522
+23:00
+8:00</t>
+        </is>
+      </c>
+      <c r="P62" s="1" t="inlineStr">
+        <is>
+          <t>13:50
+SM2512
+21:50
+8:00</t>
+        </is>
+      </c>
+      <c r="Q62" s="1" t="inlineStr">
+        <is>
+          <t>14:00
+STD5
+22:00
+8:00</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S62" s="1" t="inlineStr">
+        <is>
+          <t>7:30
+TOWN
+16:30
+8:00</t>
+        </is>
+      </c>
+      <c r="T62" s="1" t="inlineStr">
+        <is>
+          <t>14:05
+SM0517
+22:05
+8:00</t>
+        </is>
+      </c>
+      <c r="U62" s="1" t="inlineStr">
+        <is>
+          <t>12:48
+SM1504
+20:48
+8:00</t>
+        </is>
+      </c>
+      <c r="V62" s="1" t="inlineStr">
+        <is>
+          <t>13:43
+SM1512
+21:43
+8:00</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X62" s="1" t="inlineStr">
+        <is>
+          <t>14:55
+DO2W
+SM2521
+22:55
+8:00</t>
+        </is>
+      </c>
+      <c r="Y62" s="1" t="inlineStr">
+        <is>
+          <t>12:48
+SM2502
+20:48
+8:00</t>
+        </is>
+      </c>
+      <c r="Z62" s="1" t="inlineStr">
         <is>
           <t>12:40
 SM0502
@@ -11695,440 +12586,17 @@
 8:10</t>
         </is>
       </c>
-      <c r="T58" s="1" t="inlineStr">
-        <is>
-          <t>14:00
-STD5
-22:00
-8:00</t>
-        </is>
-      </c>
-      <c r="U58" s="1" t="inlineStr">
-        <is>
-          <t>13:50
-SM0512
-21:50
-8:00</t>
-        </is>
-      </c>
-      <c r="V58" s="1" t="inlineStr">
-        <is>
-          <t>13:30
-SM0508
-21:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X58" s="1" t="inlineStr">
-        <is>
-          <t>12:43
-DO2W
-SM1503
-20:43
-8:00</t>
-        </is>
-      </c>
-      <c r="Y58" s="1" t="inlineStr">
-        <is>
-          <t>12:33
-SM0504
-20:43
-8:10</t>
-        </is>
-      </c>
-      <c r="Z58" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-SM0507
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AC58" s="1" t="inlineStr">
-        <is>
-          <t>13:30
-SM0508
-21:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD58" s="1" t="inlineStr">
-        <is>
-          <t>9:30
-SM1030
-17:30
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>A021739</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>林佑任</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD6
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>15:55
-SM1529
-23:55
-8:00</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>14:35
-SM0518
-22:35
-8:00</t>
-        </is>
-      </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>12:55
-SM0505
-21:00
-8:05</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>8:15
-SM2022
-16:15
-8:00</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M59" s="1" t="inlineStr">
-        <is>
-          <t>6:47
-SM0013
-14:48
-8:01</t>
-        </is>
-      </c>
-      <c r="N59" s="1" t="inlineStr">
-        <is>
-          <t>5:02
-SM0001
-13:02
-8:00</t>
-        </is>
-      </c>
-      <c r="O59" s="1" t="inlineStr">
-        <is>
-          <t>5:27
-SM0002
-13:27
-8:00</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R59" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-STD2
-15:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S59" s="1" t="inlineStr">
-        <is>
-          <t>6:37
-SM0012
-14:43
-8:06</t>
-        </is>
-      </c>
-      <c r="T59" s="1" t="inlineStr">
-        <is>
-          <t>6:10
-SM0008
-14:10
-8:00</t>
-        </is>
-      </c>
-      <c r="U59" s="1" t="inlineStr">
-        <is>
-          <t>7:37
-SM1019
-15:43
-8:06</t>
-        </is>
-      </c>
-      <c r="V59" s="1" t="inlineStr">
-        <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>A021747</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>林美伶</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>14:10
-SM0527
-23:35
-9:25</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>13:50
-SM0512
-21:50
-8:00</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>12:50
-SM1518
-22:20
-9:30</t>
-        </is>
-      </c>
-      <c r="H60" s="1" t="inlineStr">
-        <is>
-          <t>16:25
-SM1533
-24:25
-8:00</t>
-        </is>
-      </c>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>16:15
-DO2W
-SM2534
-24:15
-8:00</t>
-        </is>
-      </c>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>14:00
-STD5
-22:00
-8:00</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr">
-        <is>
-          <t>14:15
-SM0526
-23:35
-9:20</t>
-        </is>
-      </c>
-      <c r="M60" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-SM0507
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="N60" s="1" t="inlineStr">
-        <is>
-          <t>14:15
-SM0526
-23:35
-9:20</t>
-        </is>
-      </c>
-      <c r="O60" s="1" t="inlineStr">
-        <is>
-          <t>13:43
-SM1512
-21:43
-8:00</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t>14:50
-SM2521
-22:50
-8:00</t>
-        </is>
-      </c>
-      <c r="R60" s="1" t="inlineStr">
-        <is>
-          <t>12:50
-SM2502
-20:50
-8:00</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="U60" s="1" t="inlineStr">
-        <is>
-          <t>11:50
-SM0038
-20:28
-8:38</t>
-        </is>
-      </c>
-      <c r="V60" s="1" t="inlineStr">
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AC62" s="1" t="inlineStr">
         <is>
           <t>10:40
 SM0033
@@ -12136,479 +12604,11 @@
 9:03</t>
         </is>
       </c>
-      <c r="W60" s="1" t="inlineStr">
-        <is>
-          <t>8:50
-SM2025
-16:50
-8:00</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z60" s="1" t="inlineStr">
-        <is>
-          <t>6:47
-SM0013
-14:48
-8:01</t>
-        </is>
-      </c>
-      <c r="AA60" s="1" t="inlineStr">
-        <is>
-          <t>5:27
-SM0002
-13:27
-8:00</t>
-        </is>
-      </c>
-      <c r="AB60" s="1" t="inlineStr">
-        <is>
-          <t>5:37
-SM0003
-13:37
-8:00</t>
-        </is>
-      </c>
-      <c r="AC60" s="1" t="inlineStr">
-        <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>A021794</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>狄君璞</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>5:52
-SM0004
-13:52
-8:00</t>
-        </is>
-      </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>5:02
-SM0001
-13:02
-8:00</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>12:00
-STD4
-20:00
-8:00</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>12:00
-STD4
-20:00
-8:00</t>
-        </is>
-      </c>
-      <c r="L61" s="1" t="inlineStr">
-        <is>
-          <t>16:25
-SM0533
-24:25
-8:00</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N61" s="1" t="inlineStr">
-        <is>
-          <t>15:50
-SM1535
-24:15
-8:25</t>
-        </is>
-      </c>
-      <c r="O61" s="1" t="inlineStr">
-        <is>
-          <t>15:15
-SM1523
-23:15
-8:00</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="Q61" s="1" t="inlineStr">
-        <is>
-          <t>14:15
-SM1517
-22:25
-8:10</t>
-        </is>
-      </c>
-      <c r="R61" s="1" t="inlineStr">
-        <is>
-          <t>15:15
-SM2523
-23:15
-8:00</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="U61" s="1" t="inlineStr">
-        <is>
-          <t>14:08
-SM1516
-22:08
-8:00</t>
-        </is>
-      </c>
-      <c r="V61" s="1" t="inlineStr">
-        <is>
-          <t>15:27
-SM0530
-23:55
-8:28</t>
-        </is>
-      </c>
-      <c r="W61" s="1" t="inlineStr">
-        <is>
-          <t>16:10
-SM3531
-24:10
-8:00</t>
-        </is>
-      </c>
-      <c r="X61" s="1" t="inlineStr">
-        <is>
-          <t>14:50
-DO2W
-SM1524
-22:50
-8:00</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z61" s="1" t="inlineStr">
-        <is>
-          <t>9:40
-SM0031
-17:43
-8:03</t>
-        </is>
-      </c>
-      <c r="AA61" s="1" t="inlineStr">
-        <is>
-          <t>6:27
-SM0009
-14:27
-8:00</t>
-        </is>
-      </c>
-      <c r="AB61" s="1" t="inlineStr">
-        <is>
-          <t>6:10
-SM0008
-14:10
-8:00</t>
-        </is>
-      </c>
-      <c r="AC61" s="1" t="inlineStr">
-        <is>
-          <t>7:00
-STD2
-15:00
-8:00</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>A021811</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>劉妍利</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>6:47
-SM1013
-14:47
-8:00</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>6:37
-SM0012
-14:43
-8:06</t>
-        </is>
-      </c>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>7:37
-SM0019
-16:08
-8:31</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>11:40
-SM2504
-20:48
-9:08</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-DO2W
-SM2507
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>13:08
-SM0507
-21:08
-8:00</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>13:50
-SM0512
-21:50
-8:00</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="N62" s="1" t="inlineStr">
-        <is>
-          <t>14:00
-STD5
-22:00
-8:00</t>
-        </is>
-      </c>
-      <c r="O62" s="1" t="inlineStr">
-        <is>
-          <t>15:00
-SM0522
-23:00
-8:00</t>
-        </is>
-      </c>
-      <c r="P62" s="1" t="inlineStr">
-        <is>
-          <t>13:50
-SM2512
-21:50
-8:00</t>
-        </is>
-      </c>
-      <c r="Q62" s="1" t="inlineStr">
-        <is>
-          <t>14:00
-STD5
-22:00
-8:00</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S62" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T62" s="1" t="inlineStr">
-        <is>
-          <t>14:05
-SM0517
-22:05
-8:00</t>
-        </is>
-      </c>
-      <c r="U62" s="1" t="inlineStr">
-        <is>
-          <t>12:48
-SM1504
-20:48
-8:00</t>
-        </is>
-      </c>
-      <c r="V62" s="1" t="inlineStr">
-        <is>
-          <t>13:43
-SM1512
-21:43
-8:00</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X62" s="1" t="inlineStr">
-        <is>
-          <t>14:55
-DO2W
-SM2521
-22:55
-8:00</t>
-        </is>
-      </c>
-      <c r="Y62" s="1" t="inlineStr">
-        <is>
-          <t>12:48
-SM2502
-20:48
-8:00</t>
-        </is>
-      </c>
-      <c r="Z62" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-SM0502
-20:50
-8:10</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AC62" s="1" t="inlineStr">
-        <is>
-          <t>10:40
-SM0033
-19:43
-9:03</t>
-        </is>
-      </c>
       <c r="AD62" s="1" t="inlineStr">
         <is>
-          <t>8:50
-SM2025
-16:50
+          <t>8:15
+SM1022
+16:15
 8:00</t>
         </is>
       </c>
@@ -13127,9 +13127,9 @@
       </c>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>13:00
-SM2505
-21:00
+          <t>6:10
+SM0008
+14:10
 8:00</t>
         </is>
       </c>
@@ -13698,9 +13698,9 @@
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>13:08
-SM0507
-21:08
+          <t>16:10
+SM0531
+24:10
 8:00</t>
         </is>
       </c>
@@ -13719,9 +13719,9 @@
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>6:37
-SM2012
-14:37
+          <t>16:29
+SM1534
+24:29
 8:00</t>
         </is>
       </c>
@@ -13778,9 +13778,9 @@
       </c>
       <c r="P68" s="1" t="inlineStr">
         <is>
-          <t>12:00
-STD4
-20:00
+          <t>14:00
+STD5
+22:00
 8:00</t>
         </is>
       </c>
@@ -13815,10 +13815,10 @@
       </c>
       <c r="U68" s="1" t="inlineStr">
         <is>
-          <t>14:27
-SM1518
-22:35
-8:08</t>
+          <t>15:40
+SM2531
+24:10
+8:30</t>
         </is>
       </c>
       <c r="V68" s="1" t="inlineStr">
@@ -14263,10 +14263,10 @@
       </c>
       <c r="AD70" s="1" t="inlineStr">
         <is>
-          <t>7:12
-SM2017
-15:12
-8:00</t>
+          <t>7:22
+SM0018
+16:55
+9:33</t>
         </is>
       </c>
     </row>
